--- a/backend/data/financials_by_company/1376.HK.xlsx
+++ b/backend/data/financials_by_company/1376.HK.xlsx
@@ -662,202 +662,198 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-214321.428571</v>
+        <v>-70210</v>
       </c>
       <c r="C2" t="n">
-        <v>0.370798</v>
+        <v>0.17</v>
       </c>
       <c r="D2" t="n">
-        <v>3002000</v>
+        <v>691000</v>
       </c>
       <c r="E2" t="n">
-        <v>-578000</v>
+        <v>-413000</v>
       </c>
       <c r="F2" t="n">
-        <v>-578000</v>
+        <v>-413000</v>
       </c>
       <c r="G2" t="n">
-        <v>599000</v>
+        <v>-1118000</v>
       </c>
       <c r="H2" t="n">
-        <v>895000</v>
+        <v>1009000</v>
       </c>
       <c r="I2" t="n">
-        <v>34532000</v>
+        <v>73191000</v>
       </c>
       <c r="J2" t="n">
-        <v>2424000</v>
+        <v>278000</v>
       </c>
       <c r="K2" t="n">
-        <v>1529000</v>
+        <v>-731000</v>
       </c>
       <c r="L2" t="n">
-        <v>-492000</v>
+        <v>-401000</v>
       </c>
       <c r="M2" t="n">
-        <v>577000</v>
+        <v>280000</v>
       </c>
       <c r="N2" t="n">
-        <v>142000</v>
+        <v>8000</v>
       </c>
       <c r="O2" t="n">
-        <v>962678.571429</v>
+        <v>-775210</v>
       </c>
       <c r="P2" t="n">
-        <v>-4548000</v>
+        <v>-1118000</v>
       </c>
       <c r="Q2" t="n">
-        <v>44885000</v>
+        <v>79773000</v>
       </c>
       <c r="R2" t="n">
-        <v>1444000</v>
+        <v>-610000</v>
       </c>
       <c r="S2" t="n">
-        <v>1184939000</v>
+        <v>1000000000</v>
       </c>
       <c r="T2" t="n">
         <v>1000000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0042</v>
+        <v>-0.0011</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0042</v>
+        <v>-0.0011</v>
       </c>
       <c r="W2" t="n">
-        <v>-4548000</v>
+        <v>-1118000</v>
       </c>
       <c r="X2" t="n">
-        <v>-4548000</v>
+        <v>-1118000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-4548000</v>
+        <v>-1118000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4548000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-5147000</v>
-      </c>
+        <v>-1118000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>599000</v>
+        <v>-1118000</v>
       </c>
       <c r="AD2" t="n">
-        <v>353000</v>
+        <v>107000</v>
       </c>
       <c r="AE2" t="n">
-        <v>952000</v>
+        <v>-1011000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-5000</v>
+        <v>-480000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>3000</v>
-      </c>
+        <v>-67000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>480000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-492000</v>
+        <v>-401000</v>
       </c>
       <c r="AK2" t="n">
-        <v>57000</v>
+        <v>129000</v>
       </c>
       <c r="AL2" t="n">
-        <v>577000</v>
+        <v>280000</v>
       </c>
       <c r="AM2" t="n">
-        <v>142000</v>
+        <v>8000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2235000</v>
+        <v>-197000</v>
       </c>
       <c r="AO2" t="n">
-        <v>10353000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-553000</v>
-      </c>
+        <v>6582000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>11028000</v>
+        <v>8125000</v>
       </c>
       <c r="AR2" t="n">
-        <v>11028000</v>
+        <v>8125000</v>
       </c>
       <c r="AS2" t="n">
-        <v>12588000</v>
+        <v>6385000</v>
       </c>
       <c r="AT2" t="n">
-        <v>34532000</v>
+        <v>73191000</v>
       </c>
       <c r="AU2" t="n">
-        <v>47120000</v>
+        <v>79576000</v>
       </c>
       <c r="AV2" t="n">
-        <v>47120000</v>
+        <v>79576000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-5.69395</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001423</v>
+        <v>0.010885</v>
       </c>
       <c r="D3" t="n">
-        <v>2322000</v>
+        <v>-25000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4000</v>
+        <v>-473000</v>
       </c>
       <c r="F3" t="n">
-        <v>-4000</v>
+        <v>-473000</v>
       </c>
       <c r="G3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="H3" t="n">
-        <v>787000</v>
+        <v>956000</v>
       </c>
       <c r="I3" t="n">
-        <v>79686000</v>
+        <v>58765000</v>
       </c>
       <c r="J3" t="n">
-        <v>2318000</v>
+        <v>-25000</v>
       </c>
       <c r="K3" t="n">
-        <v>1531000</v>
+        <v>-981000</v>
       </c>
       <c r="L3" t="n">
-        <v>-107000</v>
+        <v>-533000</v>
       </c>
       <c r="M3" t="n">
-        <v>126000</v>
+        <v>397000</v>
       </c>
       <c r="N3" t="n">
-        <v>69000</v>
+        <v>3000</v>
       </c>
       <c r="O3" t="n">
-        <v>1406994.30605</v>
+        <v>-1363000</v>
       </c>
       <c r="P3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="Q3" t="n">
-        <v>89649000</v>
+        <v>67338000</v>
       </c>
       <c r="R3" t="n">
-        <v>1512000</v>
+        <v>-845000</v>
       </c>
       <c r="S3" t="n">
         <v>1000000000</v>
@@ -866,142 +862,138 @@
         <v>1000000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0014</v>
+        <v>-0.0014</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0014</v>
+        <v>-0.0014</v>
       </c>
       <c r="W3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="X3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1403000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1363000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>1403000</v>
+        <v>-1363000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2000</v>
+        <v>-15000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1405000</v>
+        <v>-1378000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
+        <v>-473000</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>473000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>-533000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>139000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>397000</v>
+      </c>
+      <c r="AM3" t="n">
         <v>3000</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>-107000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>126000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>69000</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1532000</v>
+        <v>-845000</v>
       </c>
       <c r="AO3" t="n">
-        <v>9963000</v>
+        <v>8573000</v>
       </c>
       <c r="AP3" t="n">
-        <v>440000</v>
+        <v>473000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9618000</v>
+        <v>8731000</v>
       </c>
       <c r="AR3" t="n">
-        <v>9618000</v>
+        <v>8731000</v>
       </c>
       <c r="AS3" t="n">
-        <v>11495000</v>
+        <v>7728000</v>
       </c>
       <c r="AT3" t="n">
-        <v>79686000</v>
+        <v>58765000</v>
       </c>
       <c r="AU3" t="n">
-        <v>91181000</v>
+        <v>66493000</v>
       </c>
       <c r="AV3" t="n">
-        <v>91181000</v>
+        <v>66493000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-5.69395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.010885</v>
+        <v>0.001423</v>
       </c>
       <c r="D4" t="n">
-        <v>-25000</v>
+        <v>2322000</v>
       </c>
       <c r="E4" t="n">
-        <v>-473000</v>
+        <v>-4000</v>
       </c>
       <c r="F4" t="n">
-        <v>-473000</v>
+        <v>-4000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="H4" t="n">
-        <v>956000</v>
+        <v>787000</v>
       </c>
       <c r="I4" t="n">
-        <v>58765000</v>
+        <v>79686000</v>
       </c>
       <c r="J4" t="n">
-        <v>-25000</v>
+        <v>2318000</v>
       </c>
       <c r="K4" t="n">
-        <v>-981000</v>
+        <v>1531000</v>
       </c>
       <c r="L4" t="n">
-        <v>-533000</v>
+        <v>-107000</v>
       </c>
       <c r="M4" t="n">
-        <v>397000</v>
+        <v>126000</v>
       </c>
       <c r="N4" t="n">
-        <v>3000</v>
+        <v>69000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1363000</v>
+        <v>1406994.30605</v>
       </c>
       <c r="P4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="Q4" t="n">
-        <v>67338000</v>
+        <v>89649000</v>
       </c>
       <c r="R4" t="n">
-        <v>-845000</v>
+        <v>1512000</v>
       </c>
       <c r="S4" t="n">
         <v>1000000000</v>
@@ -1010,222 +1002,230 @@
         <v>1000000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0014</v>
+        <v>0.0014</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0014</v>
+        <v>0.0014</v>
       </c>
       <c r="W4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="X4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1363000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>1403000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-1363000</v>
+        <v>1403000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-15000</v>
+        <v>2000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1378000</v>
+        <v>1405000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-473000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>473000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-4000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>3000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-533000</v>
+        <v>-107000</v>
       </c>
       <c r="AK4" t="n">
-        <v>139000</v>
+        <v>50000</v>
       </c>
       <c r="AL4" t="n">
-        <v>397000</v>
+        <v>126000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3000</v>
+        <v>69000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-845000</v>
+        <v>1532000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8573000</v>
+        <v>9963000</v>
       </c>
       <c r="AP4" t="n">
-        <v>473000</v>
+        <v>440000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8731000</v>
+        <v>9618000</v>
       </c>
       <c r="AR4" t="n">
-        <v>8731000</v>
+        <v>9618000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7728000</v>
+        <v>11495000</v>
       </c>
       <c r="AT4" t="n">
-        <v>58765000</v>
+        <v>79686000</v>
       </c>
       <c r="AU4" t="n">
-        <v>66493000</v>
+        <v>91181000</v>
       </c>
       <c r="AV4" t="n">
-        <v>66493000</v>
+        <v>91181000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-70210</v>
+        <v>-214321.428571</v>
       </c>
       <c r="C5" t="n">
-        <v>0.17</v>
+        <v>0.370798</v>
       </c>
       <c r="D5" t="n">
-        <v>691000</v>
+        <v>3002000</v>
       </c>
       <c r="E5" t="n">
-        <v>-413000</v>
+        <v>-578000</v>
       </c>
       <c r="F5" t="n">
-        <v>-413000</v>
+        <v>-578000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1118000</v>
+        <v>599000</v>
       </c>
       <c r="H5" t="n">
-        <v>1009000</v>
+        <v>895000</v>
       </c>
       <c r="I5" t="n">
-        <v>73191000</v>
+        <v>34532000</v>
       </c>
       <c r="J5" t="n">
-        <v>278000</v>
+        <v>2424000</v>
       </c>
       <c r="K5" t="n">
-        <v>-731000</v>
+        <v>1529000</v>
       </c>
       <c r="L5" t="n">
-        <v>-401000</v>
+        <v>-492000</v>
       </c>
       <c r="M5" t="n">
-        <v>280000</v>
+        <v>577000</v>
       </c>
       <c r="N5" t="n">
-        <v>8000</v>
+        <v>142000</v>
       </c>
       <c r="O5" t="n">
-        <v>-775210</v>
+        <v>962678.571429</v>
       </c>
       <c r="P5" t="n">
-        <v>-1118000</v>
+        <v>-4548000</v>
       </c>
       <c r="Q5" t="n">
-        <v>79773000</v>
+        <v>44885000</v>
       </c>
       <c r="R5" t="n">
-        <v>-610000</v>
+        <v>1444000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000000000</v>
+        <v>1184939000</v>
       </c>
       <c r="T5" t="n">
         <v>1000000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0042</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0042</v>
       </c>
       <c r="W5" t="n">
-        <v>-1118000</v>
+        <v>-4548000</v>
       </c>
       <c r="X5" t="n">
-        <v>-1118000</v>
+        <v>-4548000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1118000</v>
+        <v>-4548000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1118000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-4548000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-5147000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-1118000</v>
+        <v>599000</v>
       </c>
       <c r="AD5" t="n">
-        <v>107000</v>
+        <v>353000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1011000</v>
+        <v>952000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-480000</v>
+        <v>-5000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-67000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>480000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>3000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-401000</v>
+        <v>-492000</v>
       </c>
       <c r="AK5" t="n">
-        <v>129000</v>
+        <v>57000</v>
       </c>
       <c r="AL5" t="n">
-        <v>280000</v>
+        <v>577000</v>
       </c>
       <c r="AM5" t="n">
-        <v>8000</v>
+        <v>142000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-197000</v>
+        <v>2235000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6582000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>10353000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-553000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>8125000</v>
+        <v>11028000</v>
       </c>
       <c r="AR5" t="n">
-        <v>8125000</v>
+        <v>11028000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6385000</v>
+        <v>12588000</v>
       </c>
       <c r="AT5" t="n">
-        <v>73191000</v>
+        <v>34532000</v>
       </c>
       <c r="AU5" t="n">
-        <v>79576000</v>
+        <v>47120000</v>
       </c>
       <c r="AV5" t="n">
-        <v>79576000</v>
+        <v>47120000</v>
       </c>
     </row>
   </sheetData>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1000000000</v>
@@ -1549,42 +1549,42 @@
       <c r="C2" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1251000</v>
+      </c>
       <c r="E2" t="n">
-        <v>11133000</v>
+        <v>12535000</v>
       </c>
       <c r="F2" t="n">
-        <v>8218000</v>
+        <v>12350000</v>
       </c>
       <c r="G2" t="n">
-        <v>14827000</v>
+        <v>24252000</v>
       </c>
       <c r="H2" t="n">
-        <v>5880000</v>
+        <v>12713000</v>
       </c>
       <c r="I2" t="n">
-        <v>8218000</v>
+        <v>12350000</v>
       </c>
       <c r="J2" t="n">
-        <v>4524000</v>
+        <v>633000</v>
       </c>
       <c r="K2" t="n">
-        <v>8218000</v>
+        <v>12350000</v>
       </c>
       <c r="L2" t="n">
-        <v>8218000</v>
+        <v>14933000</v>
       </c>
       <c r="M2" t="n">
-        <v>8218000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+        <v>12350000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>8218000</v>
+        <v>12350000</v>
       </c>
       <c r="P2" t="n">
-        <v>-10272000</v>
+        <v>-6158000</v>
       </c>
       <c r="Q2" t="n">
         <v>29730000</v>
@@ -1596,132 +1596,124 @@
         <v>1829000</v>
       </c>
       <c r="T2" t="n">
-        <v>30418000</v>
+        <v>45252000</v>
       </c>
       <c r="U2" t="n">
-        <v>4643000</v>
+        <v>2961000</v>
       </c>
       <c r="V2" t="n">
-        <v>39000</v>
+        <v>13000</v>
       </c>
       <c r="W2" t="n">
-        <v>4354000</v>
+        <v>2948000</v>
       </c>
       <c r="X2" t="n">
-        <v>4354000</v>
+        <v>365000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>250000</v>
-      </c>
+        <v>2583000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>25775000</v>
+        <v>42291000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6779000</v>
+        <v>9587000</v>
       </c>
       <c r="AC2" t="n">
-        <v>170000</v>
+        <v>268000</v>
       </c>
       <c r="AD2" t="n">
-        <v>6609000</v>
+        <v>9319000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36000</v>
+        <v>232000</v>
       </c>
       <c r="AF2" t="n">
-        <v>209000</v>
+        <v>898000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5246000</v>
+        <v>8281000</v>
       </c>
       <c r="AH2" t="n">
-        <v>38000</v>
+        <v>4000</v>
       </c>
       <c r="AI2" t="n">
-        <v>838000</v>
+        <v>234000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4370000</v>
+        <v>8043000</v>
       </c>
       <c r="AK2" t="n">
-        <v>38636000</v>
+        <v>57602000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6981000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>148000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
+        <v>2598000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>6833000</v>
+        <v>2598000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-8235000</v>
+        <v>-6477000</v>
       </c>
       <c r="AR2" t="n">
-        <v>15068000</v>
+        <v>9075000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2004000</v>
+        <v>522000</v>
       </c>
       <c r="AT2" t="n">
-        <v>3029000</v>
+        <v>2718000</v>
       </c>
       <c r="AU2" t="n">
-        <v>10009000</v>
+        <v>5622000</v>
       </c>
       <c r="AV2" t="n">
-        <v>26000</v>
+        <v>213000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>31655000</v>
+        <v>55004000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1988000</v>
+        <v>1827000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1023000</v>
+        <v>1117000</v>
       </c>
       <c r="BA2" t="n">
-        <v>9485000</v>
+        <v>32593000</v>
       </c>
       <c r="BB2" t="n">
-        <v>6000</v>
+        <v>17000</v>
       </c>
       <c r="BC2" t="n">
-        <v>3350000</v>
+        <v>8799000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-30000</v>
+        <v>-189000</v>
       </c>
       <c r="BE2" t="n">
-        <v>3380000</v>
+        <v>8988000</v>
       </c>
       <c r="BF2" t="n">
-        <v>15803000</v>
+        <v>10651000</v>
       </c>
       <c r="BG2" t="n">
-        <v>15803000</v>
+        <v>10651000</v>
       </c>
       <c r="BH2" t="n">
-        <v>15803000</v>
+        <v>10651000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1000000000</v>
@@ -1729,42 +1721,42 @@
       <c r="C3" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2907000</v>
+      </c>
       <c r="E3" t="n">
-        <v>1997000</v>
+        <v>7440000</v>
       </c>
       <c r="F3" t="n">
-        <v>12361000</v>
+        <v>10973000</v>
       </c>
       <c r="G3" t="n">
-        <v>13944000</v>
+        <v>17927000</v>
       </c>
       <c r="H3" t="n">
-        <v>11901000</v>
+        <v>11006000</v>
       </c>
       <c r="I3" t="n">
-        <v>12361000</v>
+        <v>10973000</v>
       </c>
       <c r="J3" t="n">
-        <v>414000</v>
+        <v>486000</v>
       </c>
       <c r="K3" t="n">
-        <v>12361000</v>
+        <v>10973000</v>
       </c>
       <c r="L3" t="n">
-        <v>12944000</v>
+        <v>12556000</v>
       </c>
       <c r="M3" t="n">
-        <v>12361000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>10973000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>12361000</v>
+        <v>10973000</v>
       </c>
       <c r="P3" t="n">
-        <v>-6118000</v>
+        <v>-7521000</v>
       </c>
       <c r="Q3" t="n">
         <v>29730000</v>
@@ -1776,130 +1768,122 @@
         <v>1829000</v>
       </c>
       <c r="T3" t="n">
-        <v>31862000</v>
+        <v>30500000</v>
       </c>
       <c r="U3" t="n">
-        <v>790000</v>
+        <v>1875000</v>
       </c>
       <c r="V3" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="W3" t="n">
-        <v>787000</v>
+        <v>1865000</v>
       </c>
       <c r="X3" t="n">
-        <v>204000</v>
+        <v>282000</v>
       </c>
       <c r="Y3" t="n">
-        <v>583000</v>
+        <v>1583000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>31072000</v>
+        <v>28625000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1210000</v>
+        <v>5575000</v>
       </c>
       <c r="AC3" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000000</v>
+        <v>5371000</v>
       </c>
       <c r="AE3" t="n">
-        <v>151000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>528000</v>
-      </c>
+        <v>144000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>7475000</v>
+        <v>8287000</v>
       </c>
       <c r="AH3" t="n">
-        <v>179000</v>
+        <v>18000</v>
       </c>
       <c r="AI3" t="n">
-        <v>634000</v>
+        <v>221000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6662000</v>
+        <v>8048000</v>
       </c>
       <c r="AK3" t="n">
-        <v>44223000</v>
+        <v>41473000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
+        <v>1842000</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>1250000</v>
+        <v>1842000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-7664000</v>
+        <v>-7103000</v>
       </c>
       <c r="AR3" t="n">
-        <v>8914000</v>
+        <v>8945000</v>
       </c>
       <c r="AS3" t="n">
-        <v>523000</v>
+        <v>522000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2736000</v>
+        <v>2653000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5563000</v>
+        <v>5620000</v>
       </c>
       <c r="AV3" t="n">
-        <v>92000</v>
+        <v>150000</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>42973000</v>
+        <v>39631000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1980000</v>
+        <v>2180000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>939000</v>
+        <v>1101000</v>
       </c>
       <c r="BA3" t="n">
-        <v>19039000</v>
+        <v>23505000</v>
       </c>
       <c r="BB3" t="n">
-        <v>9000</v>
+        <v>19000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4026000</v>
+        <v>8779000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-85000</v>
+        <v>-257000</v>
       </c>
       <c r="BE3" t="n">
-        <v>4111000</v>
+        <v>9036000</v>
       </c>
       <c r="BF3" t="n">
-        <v>16980000</v>
+        <v>4047000</v>
       </c>
       <c r="BG3" t="n">
-        <v>16980000</v>
+        <v>4047000</v>
       </c>
       <c r="BH3" t="n">
-        <v>16980000</v>
+        <v>4047000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1000000000</v>
@@ -1907,42 +1891,42 @@
       <c r="C4" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D4" t="n">
-        <v>2907000</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>7440000</v>
+        <v>1997000</v>
       </c>
       <c r="F4" t="n">
-        <v>10973000</v>
+        <v>12361000</v>
       </c>
       <c r="G4" t="n">
-        <v>17927000</v>
+        <v>13944000</v>
       </c>
       <c r="H4" t="n">
-        <v>11006000</v>
+        <v>11901000</v>
       </c>
       <c r="I4" t="n">
-        <v>10973000</v>
+        <v>12361000</v>
       </c>
       <c r="J4" t="n">
-        <v>486000</v>
+        <v>414000</v>
       </c>
       <c r="K4" t="n">
-        <v>10973000</v>
+        <v>12361000</v>
       </c>
       <c r="L4" t="n">
-        <v>12556000</v>
+        <v>12944000</v>
       </c>
       <c r="M4" t="n">
-        <v>10973000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>12361000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>10973000</v>
+        <v>12361000</v>
       </c>
       <c r="P4" t="n">
-        <v>-7521000</v>
+        <v>-6118000</v>
       </c>
       <c r="Q4" t="n">
         <v>29730000</v>
@@ -1954,122 +1938,130 @@
         <v>1829000</v>
       </c>
       <c r="T4" t="n">
-        <v>30500000</v>
+        <v>31862000</v>
       </c>
       <c r="U4" t="n">
-        <v>1875000</v>
+        <v>790000</v>
       </c>
       <c r="V4" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="W4" t="n">
-        <v>1865000</v>
+        <v>787000</v>
       </c>
       <c r="X4" t="n">
-        <v>282000</v>
+        <v>204000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1583000</v>
+        <v>583000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>28625000</v>
+        <v>31072000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5575000</v>
+        <v>1210000</v>
       </c>
       <c r="AC4" t="n">
-        <v>204000</v>
+        <v>210000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5371000</v>
+        <v>1000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>144000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>151000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>528000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>8287000</v>
+        <v>7475000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18000</v>
+        <v>179000</v>
       </c>
       <c r="AI4" t="n">
-        <v>221000</v>
+        <v>634000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8048000</v>
+        <v>6662000</v>
       </c>
       <c r="AK4" t="n">
-        <v>41473000</v>
+        <v>44223000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1842000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>1250000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP4" t="n">
-        <v>1842000</v>
+        <v>1250000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-7103000</v>
+        <v>-7664000</v>
       </c>
       <c r="AR4" t="n">
-        <v>8945000</v>
+        <v>8914000</v>
       </c>
       <c r="AS4" t="n">
-        <v>522000</v>
+        <v>523000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2653000</v>
+        <v>2736000</v>
       </c>
       <c r="AU4" t="n">
-        <v>5620000</v>
+        <v>5563000</v>
       </c>
       <c r="AV4" t="n">
-        <v>150000</v>
+        <v>92000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>39631000</v>
+        <v>42973000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2180000</v>
+        <v>1980000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1101000</v>
+        <v>939000</v>
       </c>
       <c r="BA4" t="n">
-        <v>23505000</v>
+        <v>19039000</v>
       </c>
       <c r="BB4" t="n">
-        <v>19000</v>
+        <v>9000</v>
       </c>
       <c r="BC4" t="n">
-        <v>8779000</v>
+        <v>4026000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-257000</v>
+        <v>-85000</v>
       </c>
       <c r="BE4" t="n">
-        <v>9036000</v>
+        <v>4111000</v>
       </c>
       <c r="BF4" t="n">
-        <v>4047000</v>
+        <v>16980000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4047000</v>
+        <v>16980000</v>
       </c>
       <c r="BH4" t="n">
-        <v>4047000</v>
+        <v>16980000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1000000000</v>
@@ -2077,42 +2069,42 @@
       <c r="C5" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D5" t="n">
-        <v>1251000</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>12535000</v>
+        <v>11133000</v>
       </c>
       <c r="F5" t="n">
-        <v>12350000</v>
+        <v>8218000</v>
       </c>
       <c r="G5" t="n">
-        <v>24252000</v>
+        <v>14827000</v>
       </c>
       <c r="H5" t="n">
-        <v>12713000</v>
+        <v>5880000</v>
       </c>
       <c r="I5" t="n">
-        <v>12350000</v>
+        <v>8218000</v>
       </c>
       <c r="J5" t="n">
-        <v>633000</v>
+        <v>4524000</v>
       </c>
       <c r="K5" t="n">
-        <v>12350000</v>
+        <v>8218000</v>
       </c>
       <c r="L5" t="n">
-        <v>14933000</v>
+        <v>8218000</v>
       </c>
       <c r="M5" t="n">
-        <v>12350000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>8218000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
       <c r="O5" t="n">
-        <v>12350000</v>
+        <v>8218000</v>
       </c>
       <c r="P5" t="n">
-        <v>-6158000</v>
+        <v>-10272000</v>
       </c>
       <c r="Q5" t="n">
         <v>29730000</v>
@@ -2124,119 +2116,127 @@
         <v>1829000</v>
       </c>
       <c r="T5" t="n">
-        <v>45252000</v>
+        <v>30418000</v>
       </c>
       <c r="U5" t="n">
-        <v>2961000</v>
+        <v>4643000</v>
       </c>
       <c r="V5" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="W5" t="n">
-        <v>2948000</v>
+        <v>4354000</v>
       </c>
       <c r="X5" t="n">
-        <v>365000</v>
+        <v>4354000</v>
       </c>
       <c r="Y5" t="n">
-        <v>2583000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>42291000</v>
+        <v>25775000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9587000</v>
+        <v>6779000</v>
       </c>
       <c r="AC5" t="n">
-        <v>268000</v>
+        <v>170000</v>
       </c>
       <c r="AD5" t="n">
-        <v>9319000</v>
+        <v>6609000</v>
       </c>
       <c r="AE5" t="n">
-        <v>232000</v>
+        <v>36000</v>
       </c>
       <c r="AF5" t="n">
-        <v>898000</v>
+        <v>209000</v>
       </c>
       <c r="AG5" t="n">
-        <v>8281000</v>
+        <v>5246000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4000</v>
+        <v>38000</v>
       </c>
       <c r="AI5" t="n">
-        <v>234000</v>
+        <v>838000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8043000</v>
+        <v>4370000</v>
       </c>
       <c r="AK5" t="n">
-        <v>57602000</v>
+        <v>38636000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2598000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+        <v>6981000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
       <c r="AP5" t="n">
-        <v>2598000</v>
+        <v>6833000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-6477000</v>
+        <v>-8235000</v>
       </c>
       <c r="AR5" t="n">
-        <v>9075000</v>
+        <v>15068000</v>
       </c>
       <c r="AS5" t="n">
-        <v>522000</v>
+        <v>2004000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2718000</v>
+        <v>3029000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5622000</v>
+        <v>10009000</v>
       </c>
       <c r="AV5" t="n">
-        <v>213000</v>
+        <v>26000</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>55004000</v>
+        <v>31655000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1827000</v>
+        <v>1988000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1117000</v>
+        <v>1023000</v>
       </c>
       <c r="BA5" t="n">
-        <v>32593000</v>
+        <v>9485000</v>
       </c>
       <c r="BB5" t="n">
-        <v>17000</v>
+        <v>6000</v>
       </c>
       <c r="BC5" t="n">
-        <v>8799000</v>
+        <v>3350000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-189000</v>
+        <v>-30000</v>
       </c>
       <c r="BE5" t="n">
-        <v>8988000</v>
+        <v>3380000</v>
       </c>
       <c r="BF5" t="n">
-        <v>10651000</v>
+        <v>15803000</v>
       </c>
       <c r="BG5" t="n">
-        <v>10651000</v>
+        <v>15803000</v>
       </c>
       <c r="BH5" t="n">
-        <v>10651000</v>
+        <v>15803000</v>
       </c>
     </row>
   </sheetData>
@@ -2477,486 +2477,486 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>446000</v>
+        <v>-5053000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1000000</v>
+        <v>-26823000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>24662000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-1844000</v>
+        <v>-112000</v>
       </c>
       <c r="G2" t="n">
-        <v>15803000</v>
+        <v>10651000</v>
       </c>
       <c r="H2" t="n">
-        <v>16980000</v>
+        <v>17070000</v>
       </c>
       <c r="I2" t="n">
-        <v>4000</v>
+        <v>-3000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1181000</v>
+        <v>-6416000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1487000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-94000</v>
-      </c>
+        <v>-2848000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-117000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-409000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>-1000000</v>
+        <v>-2161000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1000000</v>
+        <v>-2161000</v>
       </c>
       <c r="R2" t="n">
-        <v>-1000000</v>
+        <v>-26823000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>24662000</v>
       </c>
       <c r="T2" t="n">
-        <v>-1984000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-151000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>17000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-6000</v>
-      </c>
+        <v>1373000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>1485000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1485000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-1844000</v>
+        <v>-112000</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1844000</v>
+        <v>-112000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2290000</v>
+        <v>-4941000</v>
       </c>
       <c r="AF2" t="n">
-        <v>4000</v>
+        <v>-333000</v>
       </c>
       <c r="AG2" t="n">
-        <v>142000</v>
+        <v>8000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-169000</v>
+        <v>-6332000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4000</v>
+        <v>-401000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-10866000</v>
+        <v>-3758000</v>
       </c>
       <c r="AK2" t="n">
-        <v>10701000</v>
+        <v>-2173000</v>
       </c>
       <c r="AL2" t="n">
-        <v>492000</v>
+        <v>401000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-872000</v>
+        <v>1378000</v>
       </c>
       <c r="AN2" t="n">
-        <v>895000</v>
+        <v>1009000</v>
       </c>
       <c r="AO2" t="n">
-        <v>895000</v>
+        <v>1009000</v>
       </c>
       <c r="AP2" t="n">
-        <v>573000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183000</v>
-      </c>
+        <v>-67000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
         <v>2000</v>
       </c>
       <c r="AS2" t="n">
-        <v>952000</v>
+        <v>-1011000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>18707000</v>
+        <v>-825000</v>
       </c>
       <c r="C3" t="n">
-        <v>-6976000</v>
+        <v>-40190000</v>
       </c>
       <c r="D3" t="n">
-        <v>1605000</v>
+        <v>35242000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-54000</v>
+        <v>-113000</v>
       </c>
       <c r="G3" t="n">
-        <v>16980000</v>
+        <v>4047000</v>
       </c>
       <c r="H3" t="n">
-        <v>4047000</v>
+        <v>10651000</v>
       </c>
       <c r="I3" t="n">
-        <v>-6000</v>
+        <v>-4000</v>
       </c>
       <c r="J3" t="n">
-        <v>12939000</v>
+        <v>-6600000</v>
       </c>
       <c r="K3" t="n">
-        <v>-5770000</v>
+        <v>-5775000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-176000</v>
+        <v>-536000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-5371000</v>
+        <v>-4948000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5371000</v>
+        <v>-4948000</v>
       </c>
       <c r="R3" t="n">
-        <v>-6976000</v>
+        <v>-40190000</v>
       </c>
       <c r="S3" t="n">
-        <v>1605000</v>
+        <v>35242000</v>
       </c>
       <c r="T3" t="n">
-        <v>-52000</v>
+        <v>-113000</v>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-52000</v>
+        <v>-113000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-54000</v>
+        <v>-113000</v>
       </c>
       <c r="AE3" t="n">
-        <v>18761000</v>
+        <v>-712000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="AG3" t="n">
-        <v>69000</v>
+        <v>3000</v>
       </c>
       <c r="AH3" t="n">
-        <v>15421000</v>
+        <v>-1358000</v>
       </c>
       <c r="AI3" t="n">
-        <v>156000</v>
+        <v>-441000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6135000</v>
+        <v>-8657000</v>
       </c>
       <c r="AK3" t="n">
-        <v>9130000</v>
+        <v>7740000</v>
       </c>
       <c r="AL3" t="n">
-        <v>107000</v>
+        <v>533000</v>
       </c>
       <c r="AM3" t="n">
-        <v>968000</v>
+        <v>473000</v>
       </c>
       <c r="AN3" t="n">
-        <v>787000</v>
+        <v>956000</v>
       </c>
       <c r="AO3" t="n">
-        <v>787000</v>
+        <v>956000</v>
       </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1405000</v>
+        <v>-1378000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-825000</v>
+        <v>18707000</v>
       </c>
       <c r="C4" t="n">
-        <v>-40190000</v>
+        <v>-6976000</v>
       </c>
       <c r="D4" t="n">
-        <v>35242000</v>
+        <v>1605000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-113000</v>
+        <v>-54000</v>
       </c>
       <c r="G4" t="n">
+        <v>16980000</v>
+      </c>
+      <c r="H4" t="n">
         <v>4047000</v>
       </c>
-      <c r="H4" t="n">
-        <v>10651000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-4000</v>
+        <v>-6000</v>
       </c>
       <c r="J4" t="n">
-        <v>-6600000</v>
+        <v>12939000</v>
       </c>
       <c r="K4" t="n">
-        <v>-5775000</v>
+        <v>-5770000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-536000</v>
+        <v>-176000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-4948000</v>
+        <v>-5371000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4948000</v>
+        <v>-5371000</v>
       </c>
       <c r="R4" t="n">
-        <v>-40190000</v>
+        <v>-6976000</v>
       </c>
       <c r="S4" t="n">
-        <v>35242000</v>
+        <v>1605000</v>
       </c>
       <c r="T4" t="n">
-        <v>-113000</v>
+        <v>-52000</v>
       </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-113000</v>
+        <v>-52000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-113000</v>
+        <v>-54000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-712000</v>
+        <v>18761000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3000</v>
+        <v>69000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1358000</v>
+        <v>15421000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-441000</v>
+        <v>156000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-8657000</v>
+        <v>6135000</v>
       </c>
       <c r="AK4" t="n">
-        <v>7740000</v>
+        <v>9130000</v>
       </c>
       <c r="AL4" t="n">
-        <v>533000</v>
+        <v>107000</v>
       </c>
       <c r="AM4" t="n">
-        <v>473000</v>
+        <v>968000</v>
       </c>
       <c r="AN4" t="n">
-        <v>956000</v>
+        <v>787000</v>
       </c>
       <c r="AO4" t="n">
-        <v>956000</v>
+        <v>787000</v>
       </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1378000</v>
+        <v>1405000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-5053000</v>
+        <v>446000</v>
       </c>
       <c r="C5" t="n">
-        <v>-26823000</v>
+        <v>-1000000</v>
       </c>
       <c r="D5" t="n">
-        <v>24662000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-112000</v>
+        <v>-1844000</v>
       </c>
       <c r="G5" t="n">
-        <v>10651000</v>
+        <v>15803000</v>
       </c>
       <c r="H5" t="n">
-        <v>17070000</v>
+        <v>16980000</v>
       </c>
       <c r="I5" t="n">
-        <v>-3000</v>
+        <v>4000</v>
       </c>
       <c r="J5" t="n">
-        <v>-6416000</v>
+        <v>-1181000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2848000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-1487000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-94000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-409000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>-117000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-2161000</v>
+        <v>-1000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2161000</v>
+        <v>-1000000</v>
       </c>
       <c r="R5" t="n">
-        <v>-26823000</v>
+        <v>-1000000</v>
       </c>
       <c r="S5" t="n">
-        <v>24662000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1373000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>1485000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1485000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+        <v>-1984000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-151000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-6000</v>
+      </c>
       <c r="AB5" t="n">
-        <v>-112000</v>
+        <v>-1844000</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-112000</v>
+        <v>-1844000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4941000</v>
+        <v>2290000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-333000</v>
+        <v>4000</v>
       </c>
       <c r="AG5" t="n">
-        <v>8000</v>
+        <v>142000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-6332000</v>
+        <v>-169000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-401000</v>
+        <v>-4000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-3758000</v>
+        <v>-10866000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-2173000</v>
+        <v>10701000</v>
       </c>
       <c r="AL5" t="n">
-        <v>401000</v>
+        <v>492000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1378000</v>
+        <v>-872000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1009000</v>
+        <v>895000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1009000</v>
+        <v>895000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-67000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>573000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>183000</v>
+      </c>
       <c r="AR5" t="n">
         <v>2000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1011000</v>
+        <v>952000</v>
       </c>
     </row>
   </sheetData>
@@ -3466,187 +3466,187 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Hing Hui Ding', 'age': 54, 'title': 'Operation Director, Secretary &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 4092824, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lek Hee  Low', 'age': 59, 'title': 'GM of Human Resources &amp; Administration', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pui San  Loke', 'age': 35, 'title': 'Executive Director', 'yearBorn': 1990, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nenghuan  Zheng', 'age': 58, 'title': 'Executive Director', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Cheeric  Yu AICPA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Hing Hui Ding', 'age': 54, 'title': 'Operation Director, Secretary &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 4044127, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lek Hee  Low', 'age': 59, 'title': 'GM of Human Resources &amp; Administration', 'yearBorn': 1966, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pui San  Loke', 'age': 35, 'title': 'Executive Director', 'yearBorn': 1990, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nenghuan  Zheng', 'age': 58, 'title': 'Executive Director', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Cheeric  Yu AICPA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3778,7 +3778,7 @@
         <v>544000</v>
       </c>
       <c r="AF2" t="n">
-        <v>310666</v>
+        <v>123389</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>96000000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.05</v>
+        <v>0.066</v>
       </c>
       <c r="AN2" t="n">
         <v>0.4</v>
@@ -3814,10 +3814,10 @@
         <v>1.5073956</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.09823999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.174125</v>
+        <v>0.16377</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3855,10 +3855,10 @@
         <v>1000000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07363401</v>
+        <v>0.07275791500000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3037453</v>
+        <v>1.3194441</v>
       </c>
       <c r="BG2" t="n">
         <v>1735603200</v>
@@ -3885,10 +3885,10 @@
         <v>15.63</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.54838705</v>
+        <v>-0.020408154</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -4000,138 +4000,138 @@
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CV2" t="n">
+          <t>RAFFLESINTERIOR</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
         <v>3.2258048</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>0.096</v>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>RAFFLESINTERIOR</t>
-        </is>
-      </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1774942822</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>finmb_659526056</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
           <t>Raffles Interior Limited</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
         <v>1588815000000</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DL2" t="n">
         <v>0.0029999986</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>0.085 - 0.1</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>1774942822</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>finmb_659526056</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DN2" t="n">
-        <v>310666</v>
-      </c>
       <c r="DO2" t="n">
-        <v>0.046</v>
+        <v>123389</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.4</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
+        <v>0.030000001</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.45454547</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>0.066 - 0.4</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
         <v>-0.30400002</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="DT2" t="n">
         <v>-0.76000005</v>
       </c>
-      <c r="DT2" t="n">
-        <v>54.838707</v>
-      </c>
       <c r="DU2" t="n">
-        <v>1743159540</v>
+        <v>-2.0408154</v>
       </c>
       <c r="DV2" t="n">
         <v>1743159540</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="DW2" t="n">
+        <v>1743159540</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
         <v>0.01</v>
       </c>
-      <c r="DY2" t="n">
-        <v>-0.0022400022</v>
-      </c>
       <c r="DZ2" t="n">
-        <v>-0.022801325</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.078125</v>
+        <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.44867194</v>
+        <v>-0.06777000399999999</v>
       </c>
       <c r="EC2" t="n">
-        <v>15</v>
+        <v>-0.41381207</v>
       </c>
       <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="EE2" t="b">
-        <v>0</v>
+      <c r="EE2" t="n">
+        <v>15</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
